--- a/Result/profitability/3679.xlsx
+++ b/Result/profitability/3679.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.33</v>
       </c>
       <c r="M2" t="n">
-        <v>2.80875</v>
+        <v>2.79875</v>
       </c>
       <c r="N2" t="n">
-        <v>31.9075</v>
+        <v>31.5225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>6.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.46875</v>
+        <v>3.02</v>
       </c>
       <c r="N3" t="n">
-        <v>32.3325</v>
+        <v>31.9425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0375</v>
+        <v>2.7325</v>
       </c>
       <c r="N4" t="n">
-        <v>31.9225</v>
+        <v>31.02875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.97</v>
       </c>
       <c r="M5" t="n">
-        <v>2.79</v>
+        <v>3.2075</v>
       </c>
       <c r="N5" t="n">
-        <v>30.19125</v>
+        <v>29.87875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>99.2</v>
@@ -1137,10 +1137,10 @@
         <v>1.89</v>
       </c>
       <c r="M6" t="n">
-        <v>3.255</v>
+        <v>2.94125</v>
       </c>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>28.55125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>2.66</v>
       </c>
       <c r="M7" t="n">
-        <v>3.085</v>
+        <v>2.81875</v>
       </c>
       <c r="N7" t="n">
-        <v>28.12875</v>
+        <v>27.6175</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D69" t="n">
+        <v>753</v>
+      </c>
+      <c r="E69" t="n">
+        <v>301</v>
+      </c>
+      <c r="F69" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="G69" t="n">
+        <v>168</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>15.94%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>-21</v>
+      </c>
+      <c r="J69" t="n">
+        <v>147</v>
+      </c>
+      <c r="K69" t="n">
+        <v>95</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2.58125</v>
+      </c>
+      <c r="N69" t="n">
+        <v>31.845</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.4344569288389513</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-2.669999999999998</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.08546734955185653</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-1.825136612021858</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.08046346958480854</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
